--- a/R Markdown/resultados/df_longo_2022_2025.xlsx
+++ b/R Markdown/resultados/df_longo_2022_2025.xlsx
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B34">
-        <v>645381828.96</v>
+        <v>600441154.33</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1603,17 +1603,17 @@
         <v>0.01278087722546964</v>
       </c>
       <c r="E34">
-        <v>0.007834127496202407</v>
+        <v>0.01801978099473713</v>
       </c>
       <c r="F34">
-        <v>-0.004946749729267235</v>
+        <v>0.00523890376926749</v>
       </c>
       <c r="G34">
-        <v>-0.387043052053531</v>
+        <v>0.4099017365433602</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Abaixo do IDRGP Alvo</t>
+          <t>Acima do IDRGP Alvo</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="B35">
-        <v>3142625094.65</v>
+        <v>1086938304.9</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1640,13 +1640,13 @@
         <v>0.03138103348631988</v>
       </c>
       <c r="E35">
-        <v>0.03814753462136777</v>
+        <v>0.03261999959170723</v>
       </c>
       <c r="F35">
-        <v>0.006766501135047898</v>
+        <v>0.001238966105387353</v>
       </c>
       <c r="G35">
-        <v>0.2156239098370568</v>
+        <v>0.03948136717445787</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="B36">
-        <v>3723645915.23</v>
+        <v>1893010845.67</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1677,17 +1677,17 @@
         <v>0.07049848664210395</v>
       </c>
       <c r="E36">
-        <v>0.04520040004478207</v>
+        <v>0.05681096409472278</v>
       </c>
       <c r="F36">
-        <v>-0.02529808659732188</v>
+        <v>-0.01368752254738117</v>
       </c>
       <c r="G36">
-        <v>-0.358845810772526</v>
+        <v>-0.1941534237020989</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Abaixo do IDRGP Alvo</t>
+          <t>Dentro do IDRGP Alvo</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="B37">
-        <v>619219193.39</v>
+        <v>1726163460.9</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1714,13 +1714,13 @@
         <v>0.08227494643576272</v>
       </c>
       <c r="E37">
-        <v>0.007516545851515655</v>
+        <v>0.05180372348268497</v>
       </c>
       <c r="F37">
-        <v>-0.07475840058424707</v>
+        <v>-0.03047122295307775</v>
       </c>
       <c r="G37">
-        <v>-0.9086411334538602</v>
+        <v>-0.3703584660108964</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="B38">
-        <v>2853148426.42</v>
+        <v>842834351.62</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1751,17 +1751,17 @@
         <v>0.02290605900133662</v>
       </c>
       <c r="E38">
-        <v>0.03463365024420124</v>
+        <v>0.02529421962753502</v>
       </c>
       <c r="F38">
-        <v>0.01172759124286463</v>
+        <v>0.002388160626198399</v>
       </c>
       <c r="G38">
-        <v>0.5119864242984923</v>
+        <v>0.1042589048626411</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Acima do IDRGP Alvo</t>
+          <t>Dentro do IDRGP Alvo</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="B39">
-        <v>529096120.88</v>
+        <v>1031792894.37</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1788,13 +1788,13 @@
         <v>0.05427611013661751</v>
       </c>
       <c r="E39">
-        <v>0.006422564569875645</v>
+        <v>0.03096503604790367</v>
       </c>
       <c r="F39">
-        <v>-0.04785354556674187</v>
+        <v>-0.02331107408871384</v>
       </c>
       <c r="G39">
-        <v>-0.8816686650220601</v>
+        <v>-0.4294905075186471</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="B40">
-        <v>2236230158.87</v>
+        <v>434812479.76</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1825,17 +1825,17 @@
         <v>0.02476472440077774</v>
       </c>
       <c r="E40">
-        <v>0.02714503475201863</v>
+        <v>0.01304911497579922</v>
       </c>
       <c r="F40">
-        <v>0.002380310351240887</v>
+        <v>-0.01171560942497852</v>
       </c>
       <c r="G40">
-        <v>0.09611697318812613</v>
+        <v>-0.4730765113869223</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Abaixo do IDRGP Alvo</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="B41">
-        <v>1959834389.24</v>
+        <v>419672736.3</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1862,17 +1862,17 @@
         <v>0.01564514619986043</v>
       </c>
       <c r="E41">
-        <v>0.02378993610881432</v>
+        <v>0.01259475760955552</v>
       </c>
       <c r="F41">
-        <v>0.008144789908953891</v>
+        <v>-0.003050388590304912</v>
       </c>
       <c r="G41">
-        <v>0.5205953210604417</v>
+        <v>-0.1949734793997722</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Acima do IDRGP Alvo</t>
+          <t>Dentro do IDRGP Alvo</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="B42">
-        <v>18206639640.81</v>
+        <v>843947046.97</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1899,17 +1899,17 @@
         <v>0.04493881006046815</v>
       </c>
       <c r="E42">
-        <v>0.2210058136488974</v>
+        <v>0.02532761261929828</v>
       </c>
       <c r="F42">
-        <v>0.1760670035884292</v>
+        <v>-0.01961119744116987</v>
       </c>
       <c r="G42">
-        <v>3.917927585343702</v>
+        <v>-0.4363977910136407</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Acima do IDRGP Alvo</t>
+          <t>Abaixo do IDRGP Alvo</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="B43">
-        <v>1061808264.89</v>
+        <v>686451804.38</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1936,13 +1936,13 @@
         <v>0.03106350078710079</v>
       </c>
       <c r="E43">
-        <v>0.01288902313390865</v>
+        <v>0.0206010382352496</v>
       </c>
       <c r="F43">
-        <v>-0.01817447765319214</v>
+        <v>-0.01046246255185119</v>
       </c>
       <c r="G43">
-        <v>-0.5850749977523185</v>
+        <v>-0.3368088685031842</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="B44">
-        <v>5387841714.57</v>
+        <v>1081771738.47</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1973,17 +1973,17 @@
         <v>0.02852737800077722</v>
       </c>
       <c r="E44">
-        <v>0.06540165376102526</v>
+        <v>0.03246494626984216</v>
       </c>
       <c r="F44">
-        <v>0.03687427576024804</v>
+        <v>0.003937568269064936</v>
       </c>
       <c r="G44">
-        <v>1.292592531961522</v>
+        <v>0.138027696374958</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Acima do IDRGP Alvo</t>
+          <t>Dentro do IDRGP Alvo</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="B45">
-        <v>1566424290.79</v>
+        <v>729781207.34</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2010,13 +2010,13 @@
         <v>0.03440060917127755</v>
       </c>
       <c r="E45">
-        <v>0.01901442999560787</v>
+        <v>0.02190139272684529</v>
       </c>
       <c r="F45">
-        <v>-0.01538617917566968</v>
+        <v>-0.01249921644443226</v>
       </c>
       <c r="G45">
-        <v>-0.4472647300826352</v>
+        <v>-0.3633428809995713</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="B46">
-        <v>1921365350.61</v>
+        <v>1104357795.92</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2047,13 +2047,13 @@
         <v>0.04982071041328871</v>
       </c>
       <c r="E46">
-        <v>0.02332297013648535</v>
+        <v>0.03314277423990809</v>
       </c>
       <c r="F46">
-        <v>-0.02649774027680336</v>
+        <v>-0.01667793617338061</v>
       </c>
       <c r="G46">
-        <v>-0.5318619517263166</v>
+        <v>-0.3347590998809222</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="B47">
-        <v>1352520777.87</v>
+        <v>1149596326.06</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2084,17 +2084,17 @@
         <v>0.0146420577822676</v>
       </c>
       <c r="E47">
-        <v>0.01641790911927449</v>
+        <v>0.03450042336133822</v>
       </c>
       <c r="F47">
-        <v>0.001775851337006891</v>
+        <v>0.01985836557907062</v>
       </c>
       <c r="G47">
-        <v>0.121284273250004</v>
+        <v>1.356255102552613</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Acima do IDRGP Alvo</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="B48">
-        <v>1288212197.47</v>
+        <v>716643418.8</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2121,13 +2121,13 @@
         <v>0.03619588619759224</v>
       </c>
       <c r="E48">
-        <v>0.01563728345653274</v>
+        <v>0.02150711583469899</v>
       </c>
       <c r="F48">
-        <v>-0.0205586027410595</v>
+        <v>-0.01468877036289325</v>
       </c>
       <c r="G48">
-        <v>-0.5679817487774912</v>
+        <v>-0.4058132541004163</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B49">
-        <v>701778701.86</v>
+        <v>1105161010.6</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2158,17 +2158,17 @@
         <v>0.01196759457375883</v>
       </c>
       <c r="E49">
-        <v>0.008518714933995152</v>
+        <v>0.03316687943742992</v>
       </c>
       <c r="F49">
-        <v>-0.003448879639763678</v>
+        <v>0.02119928486367108</v>
       </c>
       <c r="G49">
-        <v>-0.288184866098822</v>
+        <v>1.771390627666686</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Acima do IDRGP Alvo</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="B50">
-        <v>2349259805.2</v>
+        <v>1414739277.9</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0.0768001000600067</v>
       </c>
       <c r="E50">
-        <v>0.02851707316473131</v>
+        <v>0.04245760266192471</v>
       </c>
       <c r="F50">
-        <v>-0.0482830268952754</v>
+        <v>-0.03434249739808199</v>
       </c>
       <c r="G50">
-        <v>-0.6286844269415029</v>
+        <v>-0.4471673522723141</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="B51">
-        <v>1205629513.93</v>
+        <v>1177863319.16</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2232,17 +2232,17 @@
         <v>0.01518693116727706</v>
       </c>
       <c r="E51">
-        <v>0.01463483305771466</v>
+        <v>0.03534874133782689</v>
       </c>
       <c r="F51">
-        <v>-0.0005520981095624034</v>
+        <v>0.02016181017054983</v>
       </c>
       <c r="G51">
-        <v>-0.03635350048546982</v>
+        <v>1.327576318643758</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Acima do IDRGP Alvo</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="B52">
-        <v>1106053510.28</v>
+        <v>599141447.25</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2269,13 +2269,13 @@
         <v>0.04188065349285796</v>
       </c>
       <c r="E52">
-        <v>0.01342610502548373</v>
+        <v>0.01798077561216131</v>
       </c>
       <c r="F52">
-        <v>-0.02845454846737423</v>
+        <v>-0.02389987788069665</v>
       </c>
       <c r="G52">
-        <v>-0.6794198775390806</v>
+        <v>-0.5706663074102312</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="B53">
-        <v>3335881874.71</v>
+        <v>1002662305.98</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2306,13 +2306,13 @@
         <v>0.03328667005479251</v>
       </c>
       <c r="E53">
-        <v>0.04049343000694954</v>
+        <v>0.03009080079728803</v>
       </c>
       <c r="F53">
-        <v>0.007206759952157034</v>
+        <v>-0.003195869257504477</v>
       </c>
       <c r="G53">
-        <v>0.2165058847969513</v>
+        <v>-0.09601048264196513</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="B54">
-        <v>1614967083.44</v>
+        <v>378277168.48</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2343,17 +2343,17 @@
         <v>0.021319194803451</v>
       </c>
       <c r="E54">
-        <v>0.01960367873112718</v>
+        <v>0.01135243925597508</v>
       </c>
       <c r="F54">
-        <v>-0.001715516072323821</v>
+        <v>-0.009966755547475921</v>
       </c>
       <c r="G54">
-        <v>-0.08046814563775764</v>
+        <v>-0.4675014999094889</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Abaixo do IDRGP Alvo</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="B55">
-        <v>1018668371.93</v>
+        <v>681661685.0599999</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2380,13 +2380,13 @@
         <v>0.006306371387863901</v>
       </c>
       <c r="E55">
-        <v>0.01236535883712209</v>
+        <v>0.02045728243093373</v>
       </c>
       <c r="F55">
-        <v>0.006058987449258186</v>
+        <v>0.01415091104306983</v>
       </c>
       <c r="G55">
-        <v>0.9607723802816649</v>
+        <v>2.243907022396763</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="B56">
-        <v>779908407.73</v>
+        <v>624679391.73</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2417,13 +2417,13 @@
         <v>0.03550998362496413</v>
       </c>
       <c r="E56">
-        <v>0.009467111758263827</v>
+        <v>0.01874719237634673</v>
       </c>
       <c r="F56">
-        <v>-0.0260428718667003</v>
+        <v>-0.0167627912486174</v>
       </c>
       <c r="G56">
-        <v>-0.733395772348138</v>
+        <v>-0.4720585462853571</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="B57">
-        <v>1152699551.01</v>
+        <v>1743044894.91</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -2454,17 +2454,17 @@
         <v>0.01442360309469943</v>
       </c>
       <c r="E57">
-        <v>0.01399232956710236</v>
+        <v>0.05231035055436987</v>
       </c>
       <c r="F57">
-        <v>-0.0004312735275970678</v>
+        <v>0.03788674745967044</v>
       </c>
       <c r="G57">
-        <v>-0.02990054043816262</v>
+        <v>2.626718664602851</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Acima do IDRGP Alvo</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="B58">
-        <v>1213834991.17</v>
+        <v>790575300.34</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -2491,13 +2491,13 @@
         <v>0.00780842708567104</v>
       </c>
       <c r="E58">
-        <v>0.01473443727955793</v>
+        <v>0.02372587833002831</v>
       </c>
       <c r="F58">
-        <v>0.006926010193886888</v>
+        <v>0.01591745124435727</v>
       </c>
       <c r="G58">
-        <v>0.8869917229036507</v>
+        <v>2.038496494840402</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="B59">
-        <v>6027832203.39</v>
+        <v>746739859.46</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -2528,17 +2528,17 @@
         <v>0.02854078087441063</v>
       </c>
       <c r="E59">
-        <v>0.07317033713696136</v>
+        <v>0.02241033718370772</v>
       </c>
       <c r="F59">
-        <v>0.04462955626255073</v>
+        <v>-0.006130443690702907</v>
       </c>
       <c r="G59">
-        <v>1.563711814996805</v>
+        <v>-0.2147959341995229</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Acima do IDRGP Alvo</t>
+          <t>Dentro do IDRGP Alvo</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2554,7 +2554,7 @@
         </is>
       </c>
       <c r="B60">
-        <v>1762950824.2</v>
+        <v>1096779160.03</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -2565,13 +2565,13 @@
         <v>0.05776210461891745</v>
       </c>
       <c r="E60">
-        <v>0.02140001609368818</v>
+        <v>0.03291533253643419</v>
       </c>
       <c r="F60">
-        <v>-0.03636208852522927</v>
+        <v>-0.02484677208248327</v>
       </c>
       <c r="G60">
-        <v>-0.6295146059016772</v>
+        <v>-0.4301569730952253</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="B61">
-        <v>1119844037.89</v>
+        <v>646056157.14</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -2602,13 +2602,13 @@
         <v>0.03997675152969091</v>
       </c>
       <c r="E61">
-        <v>0.01359350476729353</v>
+        <v>0.01938872840079512</v>
       </c>
       <c r="F61">
-        <v>-0.02638324676239738</v>
+        <v>-0.02058802312889579</v>
       </c>
       <c r="G61">
-        <v>-0.6599647483313501</v>
+        <v>-0.5149999022207939</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="B62">
-        <v>5900795535.01</v>
+        <v>4671432106.78</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2639,13 +2639,13 @@
         <v>0.01774539803593836</v>
       </c>
       <c r="E62">
-        <v>0.07162827101095119</v>
+        <v>0.1401938939210271</v>
       </c>
       <c r="F62">
-        <v>0.05388287297501283</v>
+        <v>0.1224484958850887</v>
       </c>
       <c r="G62">
-        <v>3.036442060408455</v>
+        <v>6.900295819631851</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="B63">
-        <v>856223388.3200001</v>
+        <v>885501416.5700001</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2676,17 +2676,17 @@
         <v>0.01471389456597418</v>
       </c>
       <c r="E63">
-        <v>0.01039348008935814</v>
+        <v>0.02657469675762971</v>
       </c>
       <c r="F63">
-        <v>-0.004320414476616042</v>
+        <v>0.01186080219165553</v>
       </c>
       <c r="G63">
-        <v>-0.2936282068111988</v>
+        <v>0.80609536370361</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Acima do IDRGP Alvo</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="B64">
-        <v>1981409700.4</v>
+        <v>918101079.46</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2713,13 +2713,13 @@
         <v>0.007949529934269608</v>
       </c>
       <c r="E64">
-        <v>0.02405183337770714</v>
+        <v>0.02755304206514873</v>
       </c>
       <c r="F64">
-        <v>0.01610230344343754</v>
+        <v>0.01960351213087912</v>
       </c>
       <c r="G64">
-        <v>2.025566741251223</v>
+        <v>2.465996391355216</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="B65">
-        <v>3759086816.6</v>
+        <v>490592596.61</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2750,17 +2750,17 @@
         <v>0.01470567515443555</v>
       </c>
       <c r="E65">
-        <v>0.04563060822148318</v>
+        <v>0.01472312662914672</v>
       </c>
       <c r="F65">
-        <v>0.03092493306704763</v>
+        <v>1.745147471116613E-05</v>
       </c>
       <c r="G65">
-        <v>2.102925077718719</v>
+        <v>0.001186717000606557</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Acima do IDRGP Alvo</t>
+          <t>Dentro do IDRGP Alvo</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">

--- a/R Markdown/resultados/df_longo_2022_2025.xlsx
+++ b/R Markdown/resultados/df_longo_2022_2025.xlsx
@@ -408,7 +408,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>268083860.93</v>
+        <v>270800600.28</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -419,13 +419,13 @@
         <v>0.01278087722546964</v>
       </c>
       <c r="E2">
-        <v>0.01691999650800187</v>
+        <v>0.01678909451310908</v>
       </c>
       <c r="F2">
-        <v>0.004139119282532223</v>
+        <v>0.004008217287639435</v>
       </c>
       <c r="G2">
-        <v>0.3238525188461881</v>
+        <v>0.3136104992583676</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>529830929.79</v>
+        <v>531726447.48</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -456,13 +456,13 @@
         <v>0.03138103348631988</v>
       </c>
       <c r="E3">
-        <v>0.03344004913529273</v>
+        <v>0.03296597412498709</v>
       </c>
       <c r="F3">
-        <v>0.002059015648972852</v>
+        <v>0.001584940638667209</v>
       </c>
       <c r="G3">
-        <v>0.06561337917281951</v>
+        <v>0.0505063238072813</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>1135615346.88</v>
+        <v>1136043087.37</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -493,13 +493,13 @@
         <v>0.07049848664210395</v>
       </c>
       <c r="E4">
-        <v>0.07167386965028864</v>
+        <v>0.07043239470332817</v>
       </c>
       <c r="F4">
-        <v>0.001175383008184691</v>
+        <v>-6.609193877578357E-05</v>
       </c>
       <c r="G4">
-        <v>0.01667245729900129</v>
+        <v>-0.0009374944331969723</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>901971023.1900001</v>
+        <v>903229166.3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -530,13 +530,13 @@
         <v>0.08227494643576272</v>
       </c>
       <c r="E5">
-        <v>0.05692750958506449</v>
+        <v>0.05599839817314978</v>
       </c>
       <c r="F5">
-        <v>-0.02534743685069823</v>
+        <v>-0.02627654826261294</v>
       </c>
       <c r="G5">
-        <v>-0.3080820826846552</v>
+        <v>-0.3193748449672794</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>154312005.2</v>
+        <v>156688314.62</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -567,13 +567,13 @@
         <v>0.02290605900133662</v>
       </c>
       <c r="E6">
-        <v>0.009739335221707057</v>
+        <v>0.009714361491573245</v>
       </c>
       <c r="F6">
-        <v>-0.01316672377962956</v>
+        <v>-0.01319169750976337</v>
       </c>
       <c r="G6">
-        <v>-0.5748140166259614</v>
+        <v>-0.5759042840583624</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>530860636.58</v>
+        <v>530941174.36</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -604,13 +604,13 @@
         <v>0.05427611013661751</v>
       </c>
       <c r="E7">
-        <v>0.03350503863235019</v>
+        <v>0.03291728876529197</v>
       </c>
       <c r="F7">
-        <v>-0.02077107150426732</v>
+        <v>-0.02135882137132554</v>
       </c>
       <c r="G7">
-        <v>-0.3826927068278252</v>
+        <v>-0.3935215938939544</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>318218981.72</v>
+        <v>323404422.56</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -641,13 +641,13 @@
         <v>0.02476472440077774</v>
       </c>
       <c r="E8">
-        <v>0.02008425289312066</v>
+        <v>0.0200504260725537</v>
       </c>
       <c r="F8">
-        <v>-0.004680471507657078</v>
+        <v>-0.004714298328224037</v>
       </c>
       <c r="G8">
-        <v>-0.1889975205017863</v>
+        <v>-0.1903634481018486</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>299824744.02</v>
+        <v>300184054.28</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -678,13 +678,13 @@
         <v>0.01564514619986043</v>
       </c>
       <c r="E9">
-        <v>0.01892330856558196</v>
+        <v>0.01861080977451364</v>
       </c>
       <c r="F9">
-        <v>0.003278162365721531</v>
+        <v>0.002965663574653207</v>
       </c>
       <c r="G9">
-        <v>0.2095322296029918</v>
+        <v>0.189558060804805</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>658113599.2</v>
+        <v>662096967.22</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         <v>0.04493881006046815</v>
       </c>
       <c r="E10">
-        <v>0.04153655412788948</v>
+        <v>0.0410486850767902</v>
       </c>
       <c r="F10">
-        <v>-0.003402255932578667</v>
+        <v>-0.003890124983677946</v>
       </c>
       <c r="G10">
-        <v>-0.07570863420728555</v>
+        <v>-0.08656493081244308</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>516585406.56</v>
+        <v>515288534.05</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -752,13 +752,13 @@
         <v>0.03106350078710079</v>
       </c>
       <c r="E11">
-        <v>0.03260406368648282</v>
+        <v>0.03194685643511039</v>
       </c>
       <c r="F11">
-        <v>0.001540562899382036</v>
+        <v>0.0008833556480096066</v>
       </c>
       <c r="G11">
-        <v>0.04959398845418479</v>
+        <v>0.02843709258862487</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>583297851.04</v>
+        <v>585362030.52</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -789,13 +789,13 @@
         <v>0.02852737800077722</v>
       </c>
       <c r="E12">
-        <v>0.03681459066011741</v>
+        <v>0.03629127278382752</v>
       </c>
       <c r="F12">
-        <v>0.008287212659340185</v>
+        <v>0.007763894783050302</v>
       </c>
       <c r="G12">
-        <v>0.2905003277593336</v>
+        <v>0.2721559192309499</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>677605266.5599999</v>
+        <v>677606342.2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -826,13 +826,13 @@
         <v>0.03440060917127755</v>
       </c>
       <c r="E13">
-        <v>0.04276676225202735</v>
+        <v>0.042010235243626</v>
       </c>
       <c r="F13">
-        <v>0.008366153080749804</v>
+        <v>0.007609626072348455</v>
       </c>
       <c r="G13">
-        <v>0.2431978177797805</v>
+        <v>0.2212061430209218</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>880773966.36</v>
+        <v>892661593.1899999</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -863,13 +863,13 @@
         <v>0.04982071041328871</v>
       </c>
       <c r="E14">
-        <v>0.05558966654483326</v>
+        <v>0.05534322981852083</v>
       </c>
       <c r="F14">
-        <v>0.005768956131544559</v>
+        <v>0.005522519405232122</v>
       </c>
       <c r="G14">
-        <v>0.1157943370074025</v>
+        <v>0.1108478654643812</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>288635829.29</v>
+        <v>289068585.26</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -900,13 +900,13 @@
         <v>0.0146420577822676</v>
       </c>
       <c r="E15">
-        <v>0.01821712506948048</v>
+        <v>0.01792167297148825</v>
       </c>
       <c r="F15">
-        <v>0.003575067287212888</v>
+        <v>0.003279615189220654</v>
       </c>
       <c r="G15">
-        <v>0.2441642657320003</v>
+        <v>0.2239859477396998</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>417194492.06</v>
+        <v>418653600.77</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -937,13 +937,13 @@
         <v>0.03619588619759224</v>
       </c>
       <c r="E16">
-        <v>0.02633104926318555</v>
+        <v>0.02595568423523941</v>
       </c>
       <c r="F16">
-        <v>-0.009864836934406693</v>
+        <v>-0.01024020196235283</v>
       </c>
       <c r="G16">
-        <v>-0.2725402793166839</v>
+        <v>-0.282910657483336</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="B17">
-        <v>438963711.58</v>
+        <v>439828459.44</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -974,13 +974,13 @@
         <v>0.01196759457375883</v>
       </c>
       <c r="E17">
-        <v>0.0277050041032216</v>
+        <v>0.02726848303681065</v>
       </c>
       <c r="F17">
-        <v>0.01573740952946277</v>
+        <v>0.01530088846305182</v>
       </c>
       <c r="G17">
-        <v>1.315001893861775</v>
+        <v>1.278526638644817</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>407347161.41</v>
+        <v>407603040.74</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1011,13 +1011,13 @@
         <v>0.0768001000600067</v>
       </c>
       <c r="E18">
-        <v>0.02570953926391466</v>
+        <v>0.02527057165951165</v>
       </c>
       <c r="F18">
-        <v>-0.05109056079609204</v>
+        <v>-0.05152952840049506</v>
       </c>
       <c r="G18">
-        <v>-0.6652408103136992</v>
+        <v>-0.6709565268825584</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>443362279.2</v>
+        <v>444011947.82</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1048,13 +1048,13 @@
         <v>0.01518693116727706</v>
       </c>
       <c r="E19">
-        <v>0.02798261778914968</v>
+        <v>0.02752785093235332</v>
       </c>
       <c r="F19">
-        <v>0.01279568662187262</v>
+        <v>0.01234091976507626</v>
       </c>
       <c r="G19">
-        <v>0.8425459021927486</v>
+        <v>0.8126012839030284</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>254026720.87</v>
+        <v>254092379.92</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1085,13 +1085,13 @@
         <v>0.04188065349285796</v>
       </c>
       <c r="E20">
-        <v>0.01603278621528754</v>
+        <v>0.01575321833528728</v>
       </c>
       <c r="F20">
-        <v>-0.02584786727757042</v>
+        <v>-0.02612743515757068</v>
       </c>
       <c r="G20">
-        <v>-0.6171791775402535</v>
+        <v>-0.6238545241904181</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>409432833.7</v>
+        <v>413735667.28</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1122,13 +1122,13 @@
         <v>0.03328667005479251</v>
       </c>
       <c r="E21">
-        <v>0.02584117556511241</v>
+        <v>0.02565078221475858</v>
       </c>
       <c r="F21">
-        <v>-0.007445494489680102</v>
+        <v>-0.007635887840033932</v>
       </c>
       <c r="G21">
-        <v>-0.2236779611004713</v>
+        <v>-0.2293977687604273</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>317894841.59</v>
+        <v>318856012.44</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1159,13 +1159,13 @@
         <v>0.021319194803451</v>
       </c>
       <c r="E22">
-        <v>0.0200637949295242</v>
+        <v>0.01976843376046095</v>
       </c>
       <c r="F22">
-        <v>-0.001255399873926793</v>
+        <v>-0.001550761042990043</v>
       </c>
       <c r="G22">
-        <v>-0.05888589533989238</v>
+        <v>-0.07274013194621297</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>176159856.34</v>
+        <v>179126600.35</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1196,13 +1196,13 @@
         <v>0.006306371387863901</v>
       </c>
       <c r="E23">
-        <v>0.01111825286230561</v>
+        <v>0.01110549023886406</v>
       </c>
       <c r="F23">
-        <v>0.004811881474441705</v>
+        <v>0.004799118851000157</v>
       </c>
       <c r="G23">
-        <v>0.763019045104413</v>
+        <v>0.7609952785583912</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="B24">
-        <v>367540618.45</v>
+        <v>373444861.42</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1233,13 +1233,13 @@
         <v>0.03550998362496413</v>
       </c>
       <c r="E24">
-        <v>0.02319716658492414</v>
+        <v>0.02315283299716658</v>
       </c>
       <c r="F24">
-        <v>-0.01231281704003999</v>
+        <v>-0.01235715062779755</v>
       </c>
       <c r="G24">
-        <v>-0.3467424026459947</v>
+        <v>-0.3479908849946711</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>165422674.2</v>
+        <v>166699640.05</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1270,13 +1270,13 @@
         <v>0.01442360309469943</v>
       </c>
       <c r="E25">
-        <v>0.01044058027252588</v>
+        <v>0.01033504360480332</v>
       </c>
       <c r="F25">
-        <v>-0.003983022822173549</v>
+        <v>-0.004088559489896115</v>
       </c>
       <c r="G25">
-        <v>-0.2761461748512257</v>
+        <v>-0.2834631168822602</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="B26">
-        <v>213876408.05</v>
+        <v>214276208.71</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1307,13 +1307,13 @@
         <v>0.00780842708567104</v>
       </c>
       <c r="E26">
-        <v>0.01349871665081283</v>
+        <v>0.01328469551479266</v>
       </c>
       <c r="F26">
-        <v>0.005690289565141791</v>
+        <v>0.005476268429121622</v>
       </c>
       <c r="G26">
-        <v>0.7287369789984764</v>
+        <v>0.7013279843735651</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="B27">
-        <v>297747200.45</v>
+        <v>297798794.47</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1344,13 +1344,13 @@
         <v>0.02854078087441063</v>
       </c>
       <c r="E27">
-        <v>0.01879218530501836</v>
+        <v>0.01846292844652913</v>
       </c>
       <c r="F27">
-        <v>-0.009748595569392268</v>
+        <v>-0.0100778524278815</v>
       </c>
       <c r="G27">
-        <v>-0.3415672336468116</v>
+        <v>-0.3531035983993417</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="B28">
-        <v>607742680.01</v>
+        <v>609449214.6</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         <v>0.05776210461891745</v>
       </c>
       <c r="E28">
-        <v>0.03835741542911423</v>
+        <v>0.0377846299243052</v>
       </c>
       <c r="F28">
-        <v>-0.01940468918980322</v>
+        <v>-0.01997747469461226</v>
       </c>
       <c r="G28">
-        <v>-0.3359415194066191</v>
+        <v>-0.3458578046352818</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="B29">
-        <v>451930234.72</v>
+        <v>451987454.6</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         <v>0.03997675152969091</v>
       </c>
       <c r="E29">
-        <v>0.02852338058246446</v>
+        <v>0.02802231636921318</v>
       </c>
       <c r="F29">
-        <v>-0.01145337094722645</v>
+        <v>-0.01195443516047773</v>
       </c>
       <c r="G29">
-        <v>-0.2865007913091684</v>
+        <v>-0.2990346814847905</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B30">
-        <v>2362273524.69</v>
+        <v>2593261890.04</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1455,13 +1455,13 @@
         <v>0.01774539803593836</v>
       </c>
       <c r="E30">
-        <v>0.1490938680532381</v>
+        <v>0.1607770400955828</v>
       </c>
       <c r="F30">
-        <v>0.1313484700172998</v>
+        <v>0.1430316420596444</v>
       </c>
       <c r="G30">
-        <v>7.40183284428391</v>
+        <v>8.060210414552193</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="B31">
-        <v>310130761.22</v>
+        <v>310244568.84</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1492,13 +1492,13 @@
         <v>0.01471389456597418</v>
       </c>
       <c r="E31">
-        <v>0.01957376836734131</v>
+        <v>0.01923454151522509</v>
       </c>
       <c r="F31">
-        <v>0.004859873801367128</v>
+        <v>0.004520646949250905</v>
       </c>
       <c r="G31">
-        <v>0.3302914656331414</v>
+        <v>0.3072366006825196</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         </is>
       </c>
       <c r="B32">
-        <v>268759034.4</v>
+        <v>270403481.87</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1529,13 +1529,13 @@
         <v>0.007949529934269608</v>
       </c>
       <c r="E32">
-        <v>0.01696260978846964</v>
+        <v>0.01676447396754348</v>
       </c>
       <c r="F32">
-        <v>0.009013079854200036</v>
+        <v>0.00881494403327387</v>
       </c>
       <c r="G32">
-        <v>1.133787774714272</v>
+        <v>1.108863556230356</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="B33">
-        <v>190668608.27</v>
+        <v>190978482.88</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1566,13 +1566,13 @@
         <v>0.01470567515443555</v>
       </c>
       <c r="E33">
-        <v>0.0120339664421513</v>
+        <v>0.0118402832036828</v>
       </c>
       <c r="F33">
-        <v>-0.002671708712284254</v>
+        <v>-0.002865391950752754</v>
       </c>
       <c r="G33">
-        <v>-0.1816787521978145</v>
+        <v>-0.1948493979814649</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1603,13 +1603,13 @@
         <v>0.01278087722546964</v>
       </c>
       <c r="E34">
-        <v>0.01801978099473713</v>
+        <v>0.01801978099472632</v>
       </c>
       <c r="F34">
-        <v>0.00523890376926749</v>
+        <v>0.005238903769256675</v>
       </c>
       <c r="G34">
-        <v>0.4099017365433602</v>
+        <v>0.4099017365425141</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1640,13 +1640,13 @@
         <v>0.03138103348631988</v>
       </c>
       <c r="E35">
-        <v>0.03261999959170723</v>
+        <v>0.03261999959168765</v>
       </c>
       <c r="F35">
-        <v>0.001238966105387353</v>
+        <v>0.001238966105367771</v>
       </c>
       <c r="G35">
-        <v>0.03948136717445787</v>
+        <v>0.03948136717383387</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1677,13 +1677,13 @@
         <v>0.07049848664210395</v>
       </c>
       <c r="E36">
-        <v>0.05681096409472278</v>
+        <v>0.05681096409468869</v>
       </c>
       <c r="F36">
-        <v>-0.01368752254738117</v>
+        <v>-0.01368752254741527</v>
       </c>
       <c r="G36">
-        <v>-0.1941534237020989</v>
+        <v>-0.1941534237025826</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1714,13 +1714,13 @@
         <v>0.08227494643576272</v>
       </c>
       <c r="E37">
-        <v>0.05180372348268497</v>
+        <v>0.05180372348265388</v>
       </c>
       <c r="F37">
-        <v>-0.03047122295307775</v>
+        <v>-0.03047122295310884</v>
       </c>
       <c r="G37">
-        <v>-0.3703584660108964</v>
+        <v>-0.3703584660112743</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1751,13 +1751,13 @@
         <v>0.02290605900133662</v>
       </c>
       <c r="E38">
-        <v>0.02529421962753502</v>
+        <v>0.02529421962751983</v>
       </c>
       <c r="F38">
-        <v>0.002388160626198399</v>
+        <v>0.002388160626183217</v>
       </c>
       <c r="G38">
-        <v>0.1042589048626411</v>
+        <v>0.1042589048619783</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1788,13 +1788,13 @@
         <v>0.05427611013661751</v>
       </c>
       <c r="E39">
-        <v>0.03096503604790367</v>
+        <v>0.03096503604788509</v>
       </c>
       <c r="F39">
-        <v>-0.02331107408871384</v>
+        <v>-0.02331107408873243</v>
       </c>
       <c r="G39">
-        <v>-0.4294905075186471</v>
+        <v>-0.4294905075189895</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1825,13 +1825,13 @@
         <v>0.02476472440077774</v>
       </c>
       <c r="E40">
-        <v>0.01304911497579922</v>
+        <v>0.01304911497579138</v>
       </c>
       <c r="F40">
-        <v>-0.01171560942497852</v>
+        <v>-0.01171560942498636</v>
       </c>
       <c r="G40">
-        <v>-0.4730765113869223</v>
+        <v>-0.4730765113872386</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1862,13 +1862,13 @@
         <v>0.01564514619986043</v>
       </c>
       <c r="E41">
-        <v>0.01259475760955552</v>
+        <v>0.01259475760954796</v>
       </c>
       <c r="F41">
-        <v>-0.003050388590304912</v>
+        <v>-0.003050388590312472</v>
       </c>
       <c r="G41">
-        <v>-0.1949734793997722</v>
+        <v>-0.1949734794002554</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1899,13 +1899,13 @@
         <v>0.04493881006046815</v>
       </c>
       <c r="E42">
-        <v>0.02532761261929828</v>
+        <v>0.02532761261928307</v>
       </c>
       <c r="F42">
-        <v>-0.01961119744116987</v>
+        <v>-0.01961119744118507</v>
       </c>
       <c r="G42">
-        <v>-0.4363977910136407</v>
+        <v>-0.436397791013979</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1936,13 +1936,13 @@
         <v>0.03106350078710079</v>
       </c>
       <c r="E43">
-        <v>0.0206010382352496</v>
+        <v>0.02060103823523723</v>
       </c>
       <c r="F43">
-        <v>-0.01046246255185119</v>
+        <v>-0.01046246255186355</v>
       </c>
       <c r="G43">
-        <v>-0.3368088685031842</v>
+        <v>-0.3368088685035823</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -1973,13 +1973,13 @@
         <v>0.02852737800077722</v>
       </c>
       <c r="E44">
-        <v>0.03246494626984216</v>
+        <v>0.03246494626982267</v>
       </c>
       <c r="F44">
-        <v>0.003937568269064936</v>
+        <v>0.003937568269045452</v>
       </c>
       <c r="G44">
-        <v>0.138027696374958</v>
+        <v>0.138027696374275</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2010,13 +2010,13 @@
         <v>0.03440060917127755</v>
       </c>
       <c r="E45">
-        <v>0.02190139272684529</v>
+        <v>0.02190139272683214</v>
       </c>
       <c r="F45">
-        <v>-0.01249921644443226</v>
+        <v>-0.0124992164444454</v>
       </c>
       <c r="G45">
-        <v>-0.3633428809995713</v>
+        <v>-0.3633428809999534</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2047,13 +2047,13 @@
         <v>0.04982071041328871</v>
       </c>
       <c r="E46">
-        <v>0.03314277423990809</v>
+        <v>0.0331427742398882</v>
       </c>
       <c r="F46">
-        <v>-0.01667793617338061</v>
+        <v>-0.01667793617340051</v>
       </c>
       <c r="G46">
-        <v>-0.3347590998809222</v>
+        <v>-0.3347590998813215</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2084,13 +2084,13 @@
         <v>0.0146420577822676</v>
       </c>
       <c r="E47">
-        <v>0.03450042336133822</v>
+        <v>0.03450042336131751</v>
       </c>
       <c r="F47">
-        <v>0.01985836557907062</v>
+        <v>0.01985836557904991</v>
       </c>
       <c r="G47">
-        <v>1.356255102552613</v>
+        <v>1.356255102551198</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2121,13 +2121,13 @@
         <v>0.03619588619759224</v>
       </c>
       <c r="E48">
-        <v>0.02150711583469899</v>
+        <v>0.02150711583468608</v>
       </c>
       <c r="F48">
-        <v>-0.01468877036289325</v>
+        <v>-0.01468877036290616</v>
       </c>
       <c r="G48">
-        <v>-0.4058132541004163</v>
+        <v>-0.405813254100773</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2158,13 +2158,13 @@
         <v>0.01196759457375883</v>
       </c>
       <c r="E49">
-        <v>0.03316687943742992</v>
+        <v>0.03316687943741001</v>
       </c>
       <c r="F49">
-        <v>0.02119928486367108</v>
+        <v>0.02119928486365118</v>
       </c>
       <c r="G49">
-        <v>1.771390627666686</v>
+        <v>1.771390627665023</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0.0768001000600067</v>
       </c>
       <c r="E50">
-        <v>0.04245760266192471</v>
+        <v>0.04245760266189923</v>
       </c>
       <c r="F50">
-        <v>-0.03434249739808199</v>
+        <v>-0.03434249739810748</v>
       </c>
       <c r="G50">
-        <v>-0.4471673522723141</v>
+        <v>-0.447167352272646</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2232,13 +2232,13 @@
         <v>0.01518693116727706</v>
       </c>
       <c r="E51">
-        <v>0.03534874133782689</v>
+        <v>0.03534874133780567</v>
       </c>
       <c r="F51">
-        <v>0.02016181017054983</v>
+        <v>0.02016181017052861</v>
       </c>
       <c r="G51">
-        <v>1.327576318643758</v>
+        <v>1.327576318642361</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2269,13 +2269,13 @@
         <v>0.04188065349285796</v>
       </c>
       <c r="E52">
-        <v>0.01798077561216131</v>
+        <v>0.01798077561215052</v>
       </c>
       <c r="F52">
-        <v>-0.02389987788069665</v>
+        <v>-0.02389987788070744</v>
       </c>
       <c r="G52">
-        <v>-0.5706663074102312</v>
+        <v>-0.5706663074104887</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2306,13 +2306,13 @@
         <v>0.03328667005479251</v>
       </c>
       <c r="E53">
-        <v>0.03009080079728803</v>
+        <v>0.03009080079726997</v>
       </c>
       <c r="F53">
-        <v>-0.003195869257504477</v>
+        <v>-0.003195869257522539</v>
       </c>
       <c r="G53">
-        <v>-0.09601048264196513</v>
+        <v>-0.09601048264250775</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2343,13 +2343,13 @@
         <v>0.021319194803451</v>
       </c>
       <c r="E54">
-        <v>0.01135243925597508</v>
+        <v>0.01135243925596826</v>
       </c>
       <c r="F54">
-        <v>-0.009966755547475921</v>
+        <v>-0.009966755547482735</v>
       </c>
       <c r="G54">
-        <v>-0.4675014999094889</v>
+        <v>-0.4675014999098085</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2380,13 +2380,13 @@
         <v>0.006306371387863901</v>
       </c>
       <c r="E55">
-        <v>0.02045728243093373</v>
+        <v>0.02045728243092145</v>
       </c>
       <c r="F55">
-        <v>0.01415091104306983</v>
+        <v>0.01415091104305755</v>
       </c>
       <c r="G55">
-        <v>2.243907022396763</v>
+        <v>2.243907022394816</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2417,13 +2417,13 @@
         <v>0.03550998362496413</v>
       </c>
       <c r="E56">
-        <v>0.01874719237634673</v>
+        <v>0.01874719237633548</v>
       </c>
       <c r="F56">
-        <v>-0.0167627912486174</v>
+        <v>-0.01676279124862865</v>
       </c>
       <c r="G56">
-        <v>-0.4720585462853571</v>
+        <v>-0.472058546285674</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2454,13 +2454,13 @@
         <v>0.01442360309469943</v>
       </c>
       <c r="E57">
-        <v>0.05231035055436987</v>
+        <v>0.05231035055433847</v>
       </c>
       <c r="F57">
-        <v>0.03788674745967044</v>
+        <v>0.03788674745963903</v>
       </c>
       <c r="G57">
-        <v>2.626718664602851</v>
+        <v>2.626718664600673</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2491,13 +2491,13 @@
         <v>0.00780842708567104</v>
       </c>
       <c r="E58">
-        <v>0.02372587833002831</v>
+        <v>0.02372587833001407</v>
       </c>
       <c r="F58">
-        <v>0.01591745124435727</v>
+        <v>0.01591745124434303</v>
       </c>
       <c r="G58">
-        <v>2.038496494840402</v>
+        <v>2.038496494838578</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2528,13 +2528,13 @@
         <v>0.02854078087441063</v>
       </c>
       <c r="E59">
-        <v>0.02241033718370772</v>
+        <v>0.02241033718369427</v>
       </c>
       <c r="F59">
-        <v>-0.006130443690702907</v>
+        <v>-0.006130443690716358</v>
       </c>
       <c r="G59">
-        <v>-0.2147959341995229</v>
+        <v>-0.2147959341999942</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2565,13 +2565,13 @@
         <v>0.05776210461891745</v>
       </c>
       <c r="E60">
-        <v>0.03291533253643419</v>
+        <v>0.03291533253641443</v>
       </c>
       <c r="F60">
-        <v>-0.02484677208248327</v>
+        <v>-0.02484677208250303</v>
       </c>
       <c r="G60">
-        <v>-0.4301569730952253</v>
+        <v>-0.4301569730955674</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2602,13 +2602,13 @@
         <v>0.03997675152969091</v>
       </c>
       <c r="E61">
-        <v>0.01938872840079512</v>
+        <v>0.01938872840078348</v>
       </c>
       <c r="F61">
-        <v>-0.02058802312889579</v>
+        <v>-0.02058802312890743</v>
       </c>
       <c r="G61">
-        <v>-0.5149999022207939</v>
+        <v>-0.5149999022210849</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="B62">
-        <v>4671432106.78</v>
+        <v>4671432106.8</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2639,13 +2639,13 @@
         <v>0.01774539803593836</v>
       </c>
       <c r="E62">
-        <v>0.1401938939210271</v>
+        <v>0.1401938939215432</v>
       </c>
       <c r="F62">
-        <v>0.1224484958850887</v>
+        <v>0.1224484958856048</v>
       </c>
       <c r="G62">
-        <v>6.900295819631851</v>
+        <v>6.900295819660933</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2676,13 +2676,13 @@
         <v>0.01471389456597418</v>
       </c>
       <c r="E63">
-        <v>0.02657469675762971</v>
+        <v>0.02657469675761377</v>
       </c>
       <c r="F63">
-        <v>0.01186080219165553</v>
+        <v>0.01186080219163958</v>
       </c>
       <c r="G63">
-        <v>0.80609536370361</v>
+        <v>0.806095363702526</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2713,13 +2713,13 @@
         <v>0.007949529934269608</v>
       </c>
       <c r="E64">
-        <v>0.02755304206514873</v>
+        <v>0.0275530420651322</v>
       </c>
       <c r="F64">
-        <v>0.01960351213087912</v>
+        <v>0.01960351213086259</v>
       </c>
       <c r="G64">
-        <v>2.465996391355216</v>
+        <v>2.465996391353136</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -2750,13 +2750,13 @@
         <v>0.01470567515443555</v>
       </c>
       <c r="E65">
-        <v>0.01472312662914672</v>
+        <v>0.01472312662913788</v>
       </c>
       <c r="F65">
-        <v>1.745147471116613E-05</v>
+        <v>1.745147470232772E-05</v>
       </c>
       <c r="G65">
-        <v>0.001186717000606557</v>
+        <v>0.001186717000005537</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         </is>
       </c>
       <c r="B98">
-        <v>1687158182.77</v>
+        <v>1688434491</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -3971,13 +3971,13 @@
         <v>0.05427611013661751</v>
       </c>
       <c r="E98">
-        <v>0.02959296846121103</v>
+        <v>0.02953342009533873</v>
       </c>
       <c r="F98">
-        <v>-0.02468314167540648</v>
+        <v>-0.02474269004127878</v>
       </c>
       <c r="G98">
-        <v>-0.4547699091419217</v>
+        <v>-0.455867046827773</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c r="B99">
-        <v>3031872611.37</v>
+        <v>3036975936.59</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -4008,13 +4008,13 @@
         <v>0.0768001000600067</v>
       </c>
       <c r="E99">
-        <v>0.05317943005164751</v>
+        <v>0.05312156712791723</v>
       </c>
       <c r="F99">
-        <v>-0.0236206700083592</v>
+        <v>-0.02367853293208947</v>
       </c>
       <c r="G99">
-        <v>-0.3075604066909224</v>
+        <v>-0.3083138291953861</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="B100">
-        <v>2415683562.03</v>
+        <v>2415839399.78</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -4045,13 +4045,13 @@
         <v>0.01518693116727706</v>
       </c>
       <c r="E100">
-        <v>0.04237139599207642</v>
+        <v>0.0422568955188287</v>
       </c>
       <c r="F100">
-        <v>0.02718446482479936</v>
+        <v>0.02706996435155164</v>
       </c>
       <c r="G100">
-        <v>1.789990652184762</v>
+        <v>1.78245124399317</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="B101">
-        <v>1586731172.63</v>
+        <v>1586731737.63</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -4082,13 +4082,13 @@
         <v>0.02852737800077722</v>
       </c>
       <c r="E101">
-        <v>0.02783146596898628</v>
+        <v>0.02775447625349036</v>
       </c>
       <c r="F101">
-        <v>-0.0006959120317909413</v>
+        <v>-0.0007729017472868603</v>
       </c>
       <c r="G101">
-        <v>-0.02439453186941966</v>
+        <v>-0.02709333284207903</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="B102">
-        <v>1621677779.68</v>
+        <v>1635541987.13</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -4119,13 +4119,13 @@
         <v>0.01196759457375883</v>
       </c>
       <c r="E102">
-        <v>0.02844443388795109</v>
+        <v>0.02860824559492808</v>
       </c>
       <c r="F102">
-        <v>0.01647683931419226</v>
+        <v>0.01664065102116925</v>
       </c>
       <c r="G102">
-        <v>1.376787892724975</v>
+        <v>1.390475831931753</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="B103">
-        <v>1532409954.11</v>
+        <v>1532982112.9</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0.0146420577822676</v>
       </c>
       <c r="E103">
-        <v>0.02687866490809366</v>
+        <v>0.0268143093381736</v>
       </c>
       <c r="F103">
-        <v>0.01223660712582606</v>
+        <v>0.012172251555906</v>
       </c>
       <c r="G103">
-        <v>0.8357163527004601</v>
+        <v>0.8313210982302859</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="B104">
-        <v>1000682748.19</v>
+        <v>1001849833.82</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -4193,13 +4193,13 @@
         <v>0.03106350078710079</v>
       </c>
       <c r="E104">
-        <v>0.01755210229205973</v>
+        <v>0.01752395616908264</v>
       </c>
       <c r="F104">
-        <v>-0.01351139849504105</v>
+        <v>-0.01353954461801815</v>
       </c>
       <c r="G104">
-        <v>-0.4349605856610889</v>
+        <v>-0.4358666690793745</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="B105">
-        <v>1660301401.41</v>
+        <v>1665436605.22</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -4230,13 +4230,13 @@
         <v>0.00780842708567104</v>
       </c>
       <c r="E105">
-        <v>0.02912189711065678</v>
+        <v>0.02913115028524791</v>
       </c>
       <c r="F105">
-        <v>0.02131347002498574</v>
+        <v>0.02132272319957687</v>
       </c>
       <c r="G105">
-        <v>2.729547166304122</v>
+        <v>2.730732190444017</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         </is>
       </c>
       <c r="B106">
-        <v>1077859469.28</v>
+        <v>1078636355.45</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -4267,13 +4267,13 @@
         <v>0.02854078087441063</v>
       </c>
       <c r="E106">
-        <v>0.01890579176615891</v>
+        <v>0.01886707526138185</v>
       </c>
       <c r="F106">
-        <v>-0.009634989108251717</v>
+        <v>-0.009673705613028775</v>
       </c>
       <c r="G106">
-        <v>-0.3375867377507652</v>
+        <v>-0.3389432705291578</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="B107">
-        <v>1356017191.47</v>
+        <v>1362970185.21</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -4304,13 +4304,13 @@
         <v>0.03997675152969091</v>
       </c>
       <c r="E107">
-        <v>0.02378471348439185</v>
+        <v>0.02384052876898294</v>
       </c>
       <c r="F107">
-        <v>-0.01619203804529906</v>
+        <v>-0.01613622276070797</v>
       </c>
       <c r="G107">
-        <v>-0.4050363630289761</v>
+        <v>-0.4036401694300631</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -4341,13 +4341,13 @@
         <v>0.03619588619759224</v>
       </c>
       <c r="E108">
-        <v>0.01892532493371937</v>
+        <v>0.01887296540590055</v>
       </c>
       <c r="F108">
-        <v>-0.01727056126387287</v>
+        <v>-0.01732292079169168</v>
       </c>
       <c r="G108">
-        <v>-0.477141550550618</v>
+        <v>-0.478588110735192</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="B109">
-        <v>989313791.46</v>
+        <v>990146048.22</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -4378,13 +4378,13 @@
         <v>0.02290605900133662</v>
       </c>
       <c r="E109">
-        <v>0.01735268934940643</v>
+        <v>0.01731923823736954</v>
       </c>
       <c r="F109">
-        <v>-0.005553369651930186</v>
+        <v>-0.005586820763967076</v>
       </c>
       <c r="G109">
-        <v>-0.2424410786511174</v>
+        <v>-0.2439014395117499</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="B110">
-        <v>2560599212.5</v>
+        <v>2562583888.81</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -4415,13 +4415,13 @@
         <v>0.07049848664210395</v>
       </c>
       <c r="E110">
-        <v>0.04491323487694832</v>
+        <v>0.04482369136687609</v>
       </c>
       <c r="F110">
-        <v>-0.02558525176515564</v>
+        <v>-0.02567479527522786</v>
       </c>
       <c r="G110">
-        <v>-0.362919163003356</v>
+        <v>-0.3641893109786849</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="B111">
-        <v>1202045954.4</v>
+        <v>1202924802.61</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -4452,13 +4452,13 @@
         <v>0.03440060917127755</v>
       </c>
       <c r="E111">
-        <v>0.02108403846228735</v>
+        <v>0.02104107901606681</v>
       </c>
       <c r="F111">
-        <v>-0.01331657070899019</v>
+        <v>-0.01335953015521073</v>
       </c>
       <c r="G111">
-        <v>-0.3871027586368655</v>
+        <v>-0.3883515576336115</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="B112">
-        <v>2112006389.73</v>
+        <v>2120033849.32</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -4489,13 +4489,13 @@
         <v>0.03138103348631988</v>
       </c>
       <c r="E112">
-        <v>0.03704485988299082</v>
+        <v>0.03708278326583037</v>
       </c>
       <c r="F112">
-        <v>0.005663826396670943</v>
+        <v>0.00570174977951049</v>
       </c>
       <c r="G112">
-        <v>0.1804856554243189</v>
+        <v>0.181694136427855</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="B113">
-        <v>6783905505.23</v>
+        <v>6837566518.55</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -4526,13 +4526,13 @@
         <v>0.01774539803593836</v>
       </c>
       <c r="E113">
-        <v>0.1189905627761017</v>
+        <v>0.1195999758939773</v>
       </c>
       <c r="F113">
-        <v>0.1012451647401633</v>
+        <v>0.101854577858039</v>
       </c>
       <c r="G113">
-        <v>5.705432165292625</v>
+        <v>5.739774202402272</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         </is>
       </c>
       <c r="B114">
-        <v>2038715032.19</v>
+        <v>2039768606.41</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -4563,13 +4563,13 @@
         <v>0.04982071041328871</v>
       </c>
       <c r="E114">
-        <v>0.03575932017823141</v>
+        <v>0.03567881577372384</v>
       </c>
       <c r="F114">
-        <v>-0.01406139023505729</v>
+        <v>-0.01414189463956487</v>
       </c>
       <c r="G114">
-        <v>-0.282239858051215</v>
+        <v>-0.2838557403587885</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         </is>
       </c>
       <c r="B115">
-        <v>1955065802.96</v>
+        <v>1956937590.38</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -4600,13 +4600,13 @@
         <v>0.05776210461891745</v>
       </c>
       <c r="E115">
-        <v>0.03429210209062814</v>
+        <v>0.03422996880549536</v>
       </c>
       <c r="F115">
-        <v>-0.02347000252828931</v>
+        <v>-0.02353213581342209</v>
       </c>
       <c r="G115">
-        <v>-0.4063218035965181</v>
+        <v>-0.4073974791721001</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         </is>
       </c>
       <c r="B116">
-        <v>915880639.14</v>
+        <v>918890507.58</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -4637,13 +4637,13 @@
         <v>0.021319194803451</v>
       </c>
       <c r="E116">
-        <v>0.01606466254622593</v>
+        <v>0.01607286485003414</v>
       </c>
       <c r="F116">
-        <v>-0.005254532257225067</v>
+        <v>-0.00524632995341686</v>
       </c>
       <c r="G116">
-        <v>-0.2464695456685119</v>
+        <v>-0.246084807694877</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -4674,13 +4674,13 @@
         <v>0.02476472440077774</v>
       </c>
       <c r="E117">
-        <v>0.02342024112524481</v>
+        <v>0.02335544579036864</v>
       </c>
       <c r="F117">
-        <v>-0.00134448327553293</v>
+        <v>-0.001409278610409095</v>
       </c>
       <c r="G117">
-        <v>-0.05429025794006844</v>
+        <v>-0.05690669468402548</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="B118">
-        <v>1934281944.28</v>
+        <v>1939351672.66</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -4711,13 +4711,13 @@
         <v>0.007949529934269608</v>
       </c>
       <c r="E118">
-        <v>0.03392755057394125</v>
+        <v>0.0339223629738476</v>
       </c>
       <c r="F118">
-        <v>0.02597802063967164</v>
+        <v>0.02597283303957799</v>
       </c>
       <c r="G118">
-        <v>3.267868773936312</v>
+        <v>3.267216207037825</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -4748,13 +4748,13 @@
         <v>0.01470567515443555</v>
       </c>
       <c r="E119">
-        <v>0.01361900481828035</v>
+        <v>0.01358132595864943</v>
       </c>
       <c r="F119">
-        <v>-0.001086670336155204</v>
+        <v>-0.001124349195786129</v>
       </c>
       <c r="G119">
-        <v>-0.07389462399673914</v>
+        <v>-0.07645682255173442</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         </is>
       </c>
       <c r="B120">
-        <v>996106805.3</v>
+        <v>997429393.05</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -4785,13 +4785,13 @@
         <v>0.006306371387863901</v>
       </c>
       <c r="E120">
-        <v>0.01747183967352935</v>
+        <v>0.01744663558900514</v>
       </c>
       <c r="F120">
-        <v>0.01116546828566545</v>
+        <v>0.01114026420114124</v>
       </c>
       <c r="G120">
-        <v>1.770505984971404</v>
+        <v>1.766509378527845</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         </is>
       </c>
       <c r="B121">
-        <v>1292475939.08</v>
+        <v>1294481417.88</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -4822,13 +4822,13 @@
         <v>0.04188065349285796</v>
       </c>
       <c r="E121">
-        <v>0.02267019186029855</v>
+        <v>0.0226425506726158</v>
       </c>
       <c r="F121">
-        <v>-0.01921046163255941</v>
+        <v>-0.01923810282024216</v>
       </c>
       <c r="G121">
-        <v>-0.4586953648141004</v>
+        <v>-0.4593553637725089</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="B122">
-        <v>1780968666.97</v>
+        <v>1785675753.86</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -4859,13 +4859,13 @@
         <v>0.03550998362496413</v>
       </c>
       <c r="E122">
-        <v>0.03123841624945792</v>
+        <v>0.03123432533149316</v>
       </c>
       <c r="F122">
-        <v>-0.004271567375506213</v>
+        <v>-0.004275658293470971</v>
       </c>
       <c r="G122">
-        <v>-0.1202920119766889</v>
+        <v>-0.1204072167035614</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="B123">
-        <v>2299120389.61</v>
+        <v>2301085241.03</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -4896,13 +4896,13 @@
         <v>0.04493881006046815</v>
       </c>
       <c r="E123">
-        <v>0.04032686316735905</v>
+        <v>0.04024966171964013</v>
       </c>
       <c r="F123">
-        <v>-0.004611946893109092</v>
+        <v>-0.004689148340828016</v>
       </c>
       <c r="G123">
-        <v>-0.1026272588638509</v>
+        <v>-0.1043451825831271</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         </is>
       </c>
       <c r="B124">
-        <v>1702354442.56</v>
+        <v>1705356170.99</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -4933,13 +4933,13 @@
         <v>0.03328667005479251</v>
       </c>
       <c r="E124">
-        <v>0.02985951278484731</v>
+        <v>0.02982940734656313</v>
       </c>
       <c r="F124">
-        <v>-0.003427157269945202</v>
+        <v>-0.003457262708229381</v>
       </c>
       <c r="G124">
-        <v>-0.1029588500232624</v>
+        <v>-0.1038632792808187</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         </is>
       </c>
       <c r="B125">
-        <v>985402150.88</v>
+        <v>989484961.0599999</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -4970,13 +4970,13 @@
         <v>0.01278087722546964</v>
       </c>
       <c r="E125">
-        <v>0.01728407867762847</v>
+        <v>0.01730767476545518</v>
       </c>
       <c r="F125">
-        <v>0.004503201452158826</v>
+        <v>0.004526797539985538</v>
       </c>
       <c r="G125">
-        <v>0.3523389961985456</v>
+        <v>0.3541851987252149</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         </is>
       </c>
       <c r="B126">
-        <v>1366325941.16</v>
+        <v>1376552981.17</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -5007,13 +5007,13 @@
         <v>0.01442360309469943</v>
       </c>
       <c r="E126">
-        <v>0.02396553026112693</v>
+        <v>0.0240781135975885</v>
       </c>
       <c r="F126">
-        <v>0.009541927166427499</v>
+        <v>0.009654510502889065</v>
       </c>
       <c r="G126">
-        <v>0.6615494827318208</v>
+        <v>0.6693549759724757</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="B127">
-        <v>1589744832.47</v>
+        <v>1594437761.49</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -5044,13 +5044,13 @@
         <v>0.01471389456597418</v>
       </c>
       <c r="E127">
-        <v>0.02788432594471868</v>
+        <v>0.02788926693748503</v>
       </c>
       <c r="F127">
-        <v>0.01317043137874449</v>
+        <v>0.01317537237151085</v>
       </c>
       <c r="G127">
-        <v>0.8951016550846475</v>
+        <v>0.8954374596362024</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="B128">
-        <v>1133248138.6</v>
+        <v>1144062973.34</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -5081,13 +5081,13 @@
         <v>0.01564514619986043</v>
       </c>
       <c r="E128">
-        <v>0.01987731604943867</v>
+        <v>0.02001149146577848</v>
       </c>
       <c r="F128">
-        <v>0.004232169849578239</v>
+        <v>0.004366345265918049</v>
       </c>
       <c r="G128">
-        <v>0.2705100863561117</v>
+        <v>0.2790862552602417</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         </is>
       </c>
       <c r="B129">
-        <v>3213515525.28</v>
+        <v>3217471932.62</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -5118,13 +5118,13 @@
         <v>0.08227494643576272</v>
       </c>
       <c r="E129">
-        <v>0.05636546979435603</v>
+        <v>0.05627873082286368</v>
       </c>
       <c r="F129">
-        <v>-0.02590947664140669</v>
+        <v>-0.02599621561289904</v>
       </c>
       <c r="G129">
-        <v>-0.3149133212944218</v>
+        <v>-0.3159675786990143</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
